--- a/dashboard/BuildRight_Sales_Dashboard.xlsx
+++ b/dashboard/BuildRight_Sales_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A) work\Data Analysis\Project\New folder\BuildRight_Portfolio_Project\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22584CC7-E3B1-4417-BC50-05E0728145F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE76651-C4D3-4B09-B5AA-6DCC232326D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,9 @@
     <sheet name="City_Summary" sheetId="6" r:id="rId6"/>
     <sheet name="Top10_Products" sheetId="7" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="278">
   <si>
     <t>BuildRight Hardware &amp; Materials — Sales &amp; Inventory Dashboard</t>
   </si>
@@ -862,6 +865,9 @@
   </si>
   <si>
     <t>Units Sold</t>
+  </si>
+  <si>
+    <t>Rs 8.36 Cr</t>
   </si>
 </sst>
 </file>
@@ -884,40 +890,40 @@
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF777777"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -981,7 +987,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -994,14 +1000,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2186,31 +2204,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
@@ -2262,7 +2255,25 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Revenue by Customer Segment</a:t>
+              <a:t>Revenue by Customer</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Segment</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2488,8 +2499,69 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Revenue by City</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2497,22 +2569,232 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]City_Summary!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]City_Summary!$A$3:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Faridabad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Gurgaon</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Noida</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Delhi</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Ghaziabad</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]City_Summary!$B$3:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20924301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20748305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17854152</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14517821</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9560562</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8026-4742-88F7-880DB589E5B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="21306167"/>
+        <c:axId val="72856703"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="21306167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="72856703"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="72856703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="878787"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="21306167"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
@@ -2540,16 +2822,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>41040</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>195719</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>77704</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>469728</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>130480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2577,15 +2859,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>151525</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>65313</xdr:rowOff>
+      <xdr:colOff>208767</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>39216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>281214</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>119742</xdr:rowOff>
+      <xdr:colOff>437792</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>26096</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2613,15 +2895,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>152403</xdr:colOff>
+      <xdr:colOff>152402</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>55927</xdr:rowOff>
+      <xdr:rowOff>86588</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>145142</xdr:rowOff>
+      <xdr:colOff>156576</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>130479</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2646,7 +2928,119 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52191</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>52193</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>156574</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>26095</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D037BBEE-558F-4780-ADCC-E5869A1F15EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dashboard"/>
+      <sheetName val="Sales_Clean_Sample"/>
+      <sheetName val="Category_Summary"/>
+      <sheetName val="Monthly_Summary"/>
+      <sheetName val="Customer_Segment"/>
+      <sheetName val="City_Summary"/>
+      <sheetName val="Top10_Products"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>Revenue</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Faridabad</v>
+          </cell>
+          <cell r="B3">
+            <v>20924301</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Gurgaon</v>
+          </cell>
+          <cell r="B4">
+            <v>20748305</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Noida</v>
+          </cell>
+          <cell r="B5">
+            <v>17854152</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Delhi</v>
+          </cell>
+          <cell r="B6">
+            <v>14517821</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Ghaziabad</v>
+          </cell>
+          <cell r="B7">
+            <v>9560562</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2828,11 +3222,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O15"/>
+  <dimension ref="B1:O15"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2843,79 +3237,96 @@
     <col min="13" max="13" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+    <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="D6" s="10">
-        <v>83605141</v>
+    <row r="6" spans="2:15" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="D9" s="11">
+      <c r="B9" s="14">
         <v>0.25905813614978501</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D11" s="9" t="s">
+      <c r="B11" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="D12" s="10">
+      <c r="B12" s="15">
         <v>9534</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D14" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="D15" s="12">
+      <c r="B15" s="16">
         <v>40</v>
       </c>
     </row>
